--- a/bd.xlsx
+++ b/bd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergioruiz\Reportes\AQP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F070961-3CF7-403B-97DD-E456E409E280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484C93EE-B1BF-4A43-A772-1428F7BA4146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{BD033360-FD06-4D32-9ED2-A04E63C0286B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BD033360-FD06-4D32-9ED2-A04E63C0286B}"/>
   </bookViews>
   <sheets>
     <sheet name="Pedido" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="335">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1027,6 +1027,24 @@
   </si>
   <si>
     <t>MUFFIN DE BERRIES - CONGELADO - (C16)</t>
+  </si>
+  <si>
+    <t>M9110027</t>
+  </si>
+  <si>
+    <t>BASE TORTA DE ZANAHORIA 12P RELLENA</t>
+  </si>
+  <si>
+    <t>M7020024</t>
+  </si>
+  <si>
+    <t>PAN DE YEMA</t>
+  </si>
+  <si>
+    <t>M9110242</t>
+  </si>
+  <si>
+    <t>AQP -  BASE TRES LECHES 12P</t>
   </si>
 </sst>
 </file>
@@ -2054,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE566383-DF02-41BC-AAA0-951645C6972E}">
-  <dimension ref="A1:F206"/>
+  <dimension ref="A1:F228"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="41.5546875" customWidth="1"/>
@@ -6180,6 +6198,446 @@
         <v>7</v>
       </c>
     </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>260013668</v>
+      </c>
+      <c r="B207">
+        <v>46161</v>
+      </c>
+      <c r="C207" t="s">
+        <v>229</v>
+      </c>
+      <c r="D207" t="s">
+        <v>230</v>
+      </c>
+      <c r="E207">
+        <v>187</v>
+      </c>
+      <c r="F207" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>260013699</v>
+      </c>
+      <c r="B208">
+        <v>46162</v>
+      </c>
+      <c r="C208" t="s">
+        <v>303</v>
+      </c>
+      <c r="D208" t="s">
+        <v>304</v>
+      </c>
+      <c r="E208">
+        <v>42</v>
+      </c>
+      <c r="F208" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>260013700</v>
+      </c>
+      <c r="B209">
+        <v>46162</v>
+      </c>
+      <c r="C209" t="s">
+        <v>255</v>
+      </c>
+      <c r="D209" t="s">
+        <v>256</v>
+      </c>
+      <c r="E209">
+        <v>27</v>
+      </c>
+      <c r="F209" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>260013700</v>
+      </c>
+      <c r="B210">
+        <v>46162</v>
+      </c>
+      <c r="C210" t="s">
+        <v>207</v>
+      </c>
+      <c r="D210" t="s">
+        <v>208</v>
+      </c>
+      <c r="E210">
+        <v>584</v>
+      </c>
+      <c r="F210" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>260013700</v>
+      </c>
+      <c r="B211">
+        <v>46162</v>
+      </c>
+      <c r="C211" t="s">
+        <v>171</v>
+      </c>
+      <c r="D211" t="s">
+        <v>172</v>
+      </c>
+      <c r="E211">
+        <v>6</v>
+      </c>
+      <c r="F211" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>260013700</v>
+      </c>
+      <c r="B212">
+        <v>46162</v>
+      </c>
+      <c r="C212" t="s">
+        <v>331</v>
+      </c>
+      <c r="D212" t="s">
+        <v>332</v>
+      </c>
+      <c r="E212">
+        <v>170</v>
+      </c>
+      <c r="F212" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>260013700</v>
+      </c>
+      <c r="B213">
+        <v>46162</v>
+      </c>
+      <c r="C213" t="s">
+        <v>329</v>
+      </c>
+      <c r="D213" t="s">
+        <v>330</v>
+      </c>
+      <c r="E213">
+        <v>165</v>
+      </c>
+      <c r="F213" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>260013701</v>
+      </c>
+      <c r="B214">
+        <v>46162</v>
+      </c>
+      <c r="C214" t="s">
+        <v>30</v>
+      </c>
+      <c r="D214" t="s">
+        <v>31</v>
+      </c>
+      <c r="E214">
+        <v>8</v>
+      </c>
+      <c r="F214" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>260013701</v>
+      </c>
+      <c r="B215">
+        <v>46162</v>
+      </c>
+      <c r="C215" t="s">
+        <v>5</v>
+      </c>
+      <c r="D215" t="s">
+        <v>6</v>
+      </c>
+      <c r="E215">
+        <v>16</v>
+      </c>
+      <c r="F215" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>260013701</v>
+      </c>
+      <c r="B216">
+        <v>46162</v>
+      </c>
+      <c r="C216" t="s">
+        <v>26</v>
+      </c>
+      <c r="D216" t="s">
+        <v>27</v>
+      </c>
+      <c r="E216">
+        <v>30</v>
+      </c>
+      <c r="F216" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>260013701</v>
+      </c>
+      <c r="B217">
+        <v>46162</v>
+      </c>
+      <c r="C217" t="s">
+        <v>15</v>
+      </c>
+      <c r="D217" t="s">
+        <v>16</v>
+      </c>
+      <c r="E217">
+        <v>8</v>
+      </c>
+      <c r="F217" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>260013701</v>
+      </c>
+      <c r="B218">
+        <v>46162</v>
+      </c>
+      <c r="C218" t="s">
+        <v>52</v>
+      </c>
+      <c r="D218" t="s">
+        <v>53</v>
+      </c>
+      <c r="E218">
+        <v>60</v>
+      </c>
+      <c r="F218" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>260013701</v>
+      </c>
+      <c r="B219">
+        <v>46162</v>
+      </c>
+      <c r="C219" t="s">
+        <v>48</v>
+      </c>
+      <c r="D219" t="s">
+        <v>49</v>
+      </c>
+      <c r="E219">
+        <v>24</v>
+      </c>
+      <c r="F219" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>260013701</v>
+      </c>
+      <c r="B220">
+        <v>46162</v>
+      </c>
+      <c r="C220" t="s">
+        <v>42</v>
+      </c>
+      <c r="D220" t="s">
+        <v>43</v>
+      </c>
+      <c r="E220">
+        <v>10</v>
+      </c>
+      <c r="F220" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>260013701</v>
+      </c>
+      <c r="B221">
+        <v>46162</v>
+      </c>
+      <c r="C221" t="s">
+        <v>36</v>
+      </c>
+      <c r="D221" t="s">
+        <v>37</v>
+      </c>
+      <c r="E221">
+        <v>2</v>
+      </c>
+      <c r="F221" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>260013701</v>
+      </c>
+      <c r="B222">
+        <v>46162</v>
+      </c>
+      <c r="C222" t="s">
+        <v>40</v>
+      </c>
+      <c r="D222" t="s">
+        <v>41</v>
+      </c>
+      <c r="E222">
+        <v>8</v>
+      </c>
+      <c r="F222" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>260013701</v>
+      </c>
+      <c r="B223">
+        <v>46162</v>
+      </c>
+      <c r="C223" t="s">
+        <v>28</v>
+      </c>
+      <c r="D223" t="s">
+        <v>29</v>
+      </c>
+      <c r="E223">
+        <v>6</v>
+      </c>
+      <c r="F223" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>260013701</v>
+      </c>
+      <c r="B224">
+        <v>46162</v>
+      </c>
+      <c r="C224" t="s">
+        <v>333</v>
+      </c>
+      <c r="D224" t="s">
+        <v>334</v>
+      </c>
+      <c r="E224">
+        <v>8</v>
+      </c>
+      <c r="F224" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>260013701</v>
+      </c>
+      <c r="B225">
+        <v>46162</v>
+      </c>
+      <c r="C225" t="s">
+        <v>66</v>
+      </c>
+      <c r="D225" t="s">
+        <v>67</v>
+      </c>
+      <c r="E225">
+        <v>8</v>
+      </c>
+      <c r="F225" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>260013701</v>
+      </c>
+      <c r="B226">
+        <v>46162</v>
+      </c>
+      <c r="C226" t="s">
+        <v>8</v>
+      </c>
+      <c r="D226" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226">
+        <v>36</v>
+      </c>
+      <c r="F226" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>260013702</v>
+      </c>
+      <c r="B227">
+        <v>46162</v>
+      </c>
+      <c r="C227" t="s">
+        <v>301</v>
+      </c>
+      <c r="D227" t="s">
+        <v>302</v>
+      </c>
+      <c r="E227">
+        <v>18</v>
+      </c>
+      <c r="F227" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>260013702</v>
+      </c>
+      <c r="B228">
+        <v>46162</v>
+      </c>
+      <c r="C228" t="s">
+        <v>303</v>
+      </c>
+      <c r="D228" t="s">
+        <v>304</v>
+      </c>
+      <c r="E228">
+        <v>10</v>
+      </c>
+      <c r="F228" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F206" xr:uid="{AE566383-DF02-41BC-AAA0-951645C6972E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bd.xlsx
+++ b/bd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergioruiz\Reportes\AQP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484C93EE-B1BF-4A43-A772-1428F7BA4146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB911474-11CB-4886-85BE-65DA5C7C485B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BD033360-FD06-4D32-9ED2-A04E63C0286B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{BD033360-FD06-4D32-9ED2-A04E63C0286B}"/>
   </bookViews>
   <sheets>
     <sheet name="Pedido" sheetId="1" r:id="rId1"/>
@@ -6202,7 +6202,7 @@
       <c r="A207">
         <v>260013668</v>
       </c>
-      <c r="B207">
+      <c r="B207" s="5">
         <v>46161</v>
       </c>
       <c r="C207" t="s">
@@ -6222,7 +6222,7 @@
       <c r="A208">
         <v>260013699</v>
       </c>
-      <c r="B208">
+      <c r="B208" s="5">
         <v>46162</v>
       </c>
       <c r="C208" t="s">
@@ -6242,7 +6242,7 @@
       <c r="A209">
         <v>260013700</v>
       </c>
-      <c r="B209">
+      <c r="B209" s="5">
         <v>46162</v>
       </c>
       <c r="C209" t="s">
@@ -6262,7 +6262,7 @@
       <c r="A210">
         <v>260013700</v>
       </c>
-      <c r="B210">
+      <c r="B210" s="5">
         <v>46162</v>
       </c>
       <c r="C210" t="s">
@@ -6282,7 +6282,7 @@
       <c r="A211">
         <v>260013700</v>
       </c>
-      <c r="B211">
+      <c r="B211" s="5">
         <v>46162</v>
       </c>
       <c r="C211" t="s">
@@ -6302,7 +6302,7 @@
       <c r="A212">
         <v>260013700</v>
       </c>
-      <c r="B212">
+      <c r="B212" s="5">
         <v>46162</v>
       </c>
       <c r="C212" t="s">
@@ -6322,7 +6322,7 @@
       <c r="A213">
         <v>260013700</v>
       </c>
-      <c r="B213">
+      <c r="B213" s="5">
         <v>46162</v>
       </c>
       <c r="C213" t="s">
@@ -6342,7 +6342,7 @@
       <c r="A214">
         <v>260013701</v>
       </c>
-      <c r="B214">
+      <c r="B214" s="5">
         <v>46162</v>
       </c>
       <c r="C214" t="s">
@@ -6362,7 +6362,7 @@
       <c r="A215">
         <v>260013701</v>
       </c>
-      <c r="B215">
+      <c r="B215" s="5">
         <v>46162</v>
       </c>
       <c r="C215" t="s">
@@ -6382,7 +6382,7 @@
       <c r="A216">
         <v>260013701</v>
       </c>
-      <c r="B216">
+      <c r="B216" s="5">
         <v>46162</v>
       </c>
       <c r="C216" t="s">
@@ -6402,7 +6402,7 @@
       <c r="A217">
         <v>260013701</v>
       </c>
-      <c r="B217">
+      <c r="B217" s="5">
         <v>46162</v>
       </c>
       <c r="C217" t="s">
@@ -6422,7 +6422,7 @@
       <c r="A218">
         <v>260013701</v>
       </c>
-      <c r="B218">
+      <c r="B218" s="5">
         <v>46162</v>
       </c>
       <c r="C218" t="s">
@@ -6442,7 +6442,7 @@
       <c r="A219">
         <v>260013701</v>
       </c>
-      <c r="B219">
+      <c r="B219" s="5">
         <v>46162</v>
       </c>
       <c r="C219" t="s">
@@ -6462,7 +6462,7 @@
       <c r="A220">
         <v>260013701</v>
       </c>
-      <c r="B220">
+      <c r="B220" s="5">
         <v>46162</v>
       </c>
       <c r="C220" t="s">
@@ -6482,7 +6482,7 @@
       <c r="A221">
         <v>260013701</v>
       </c>
-      <c r="B221">
+      <c r="B221" s="5">
         <v>46162</v>
       </c>
       <c r="C221" t="s">
@@ -6502,7 +6502,7 @@
       <c r="A222">
         <v>260013701</v>
       </c>
-      <c r="B222">
+      <c r="B222" s="5">
         <v>46162</v>
       </c>
       <c r="C222" t="s">
@@ -6522,7 +6522,7 @@
       <c r="A223">
         <v>260013701</v>
       </c>
-      <c r="B223">
+      <c r="B223" s="5">
         <v>46162</v>
       </c>
       <c r="C223" t="s">
@@ -6542,7 +6542,7 @@
       <c r="A224">
         <v>260013701</v>
       </c>
-      <c r="B224">
+      <c r="B224" s="5">
         <v>46162</v>
       </c>
       <c r="C224" t="s">
@@ -6562,7 +6562,7 @@
       <c r="A225">
         <v>260013701</v>
       </c>
-      <c r="B225">
+      <c r="B225" s="5">
         <v>46162</v>
       </c>
       <c r="C225" t="s">
@@ -6582,7 +6582,7 @@
       <c r="A226">
         <v>260013701</v>
       </c>
-      <c r="B226">
+      <c r="B226" s="5">
         <v>46162</v>
       </c>
       <c r="C226" t="s">
@@ -6602,7 +6602,7 @@
       <c r="A227">
         <v>260013702</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="5">
         <v>46162</v>
       </c>
       <c r="C227" t="s">
@@ -6622,7 +6622,7 @@
       <c r="A228">
         <v>260013702</v>
       </c>
-      <c r="B228">
+      <c r="B228" s="5">
         <v>46162</v>
       </c>
       <c r="C228" t="s">

--- a/bd.xlsx
+++ b/bd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergioruiz\Reportes\AQP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB911474-11CB-4886-85BE-65DA5C7C485B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511E39B2-2362-4B5F-A3E4-AAFC80C35081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{BD033360-FD06-4D32-9ED2-A04E63C0286B}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Entregas" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Entregas!$A$1:$F$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Entregas!$A$1:$F$249</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="339">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -1041,10 +1041,22 @@
     <t>PAN DE YEMA</t>
   </si>
   <si>
-    <t>M9110242</t>
-  </si>
-  <si>
-    <t>AQP -  BASE TRES LECHES 12P</t>
+    <t>M9110252</t>
+  </si>
+  <si>
+    <t>PACK CUCHAREABLE  CHOCO LUCUMA</t>
+  </si>
+  <si>
+    <t>PACK CUCHAREABLE TRES LECHES  DE FRESA</t>
+  </si>
+  <si>
+    <t>AQP - BASE TORTA CHOCOLATE 1 RELLENO</t>
+  </si>
+  <si>
+    <t>M9110255</t>
+  </si>
+  <si>
+    <t>AQP -  CUCHAREABLE TRES LECHES</t>
   </si>
 </sst>
 </file>
@@ -2072,7 +2084,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE566383-DF02-41BC-AAA0-951645C6972E}">
-  <dimension ref="A1:F228"/>
+  <dimension ref="A1:F256"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="41.5546875" customWidth="1"/>
@@ -6546,10 +6558,10 @@
         <v>46162</v>
       </c>
       <c r="C224" t="s">
-        <v>333</v>
+        <v>66</v>
       </c>
       <c r="D224" t="s">
-        <v>334</v>
+        <v>67</v>
       </c>
       <c r="E224">
         <v>8</v>
@@ -6560,86 +6572,646 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225">
-        <v>260013701</v>
+        <v>260013702</v>
       </c>
       <c r="B225" s="5">
         <v>46162</v>
       </c>
       <c r="C225" t="s">
-        <v>66</v>
+        <v>301</v>
       </c>
       <c r="D225" t="s">
-        <v>67</v>
+        <v>302</v>
       </c>
       <c r="E225">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F225" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226">
-        <v>260013701</v>
+        <v>260013702</v>
       </c>
       <c r="B226" s="5">
         <v>46162</v>
       </c>
       <c r="C226" t="s">
-        <v>8</v>
+        <v>303</v>
       </c>
       <c r="D226" t="s">
-        <v>9</v>
+        <v>304</v>
       </c>
       <c r="E226">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F226" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227">
-        <v>260013702</v>
+        <v>260013704</v>
       </c>
       <c r="B227" s="5">
         <v>46162</v>
       </c>
       <c r="C227" t="s">
-        <v>301</v>
+        <v>231</v>
       </c>
       <c r="D227" t="s">
-        <v>302</v>
+        <v>232</v>
       </c>
       <c r="E227">
-        <v>18</v>
+        <v>912</v>
       </c>
       <c r="F227" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228">
-        <v>260013702</v>
+        <v>260013704</v>
       </c>
       <c r="B228" s="5">
         <v>46162</v>
       </c>
       <c r="C228" t="s">
-        <v>303</v>
+        <v>239</v>
       </c>
       <c r="D228" t="s">
-        <v>304</v>
+        <v>240</v>
       </c>
       <c r="E228">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F228" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>260013704</v>
+      </c>
+      <c r="B229" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C229" t="s">
+        <v>227</v>
+      </c>
+      <c r="D229" t="s">
+        <v>228</v>
+      </c>
+      <c r="E229">
+        <v>34</v>
+      </c>
+      <c r="F229" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>260013704</v>
+      </c>
+      <c r="B230" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C230" t="s">
+        <v>177</v>
+      </c>
+      <c r="D230" t="s">
+        <v>178</v>
+      </c>
+      <c r="E230">
+        <v>738</v>
+      </c>
+      <c r="F230" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>260013704</v>
+      </c>
+      <c r="B231" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C231" t="s">
+        <v>329</v>
+      </c>
+      <c r="D231" t="s">
+        <v>330</v>
+      </c>
+      <c r="E231">
+        <v>330</v>
+      </c>
+      <c r="F231" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>260013704</v>
+      </c>
+      <c r="B232" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C232" t="s">
+        <v>333</v>
+      </c>
+      <c r="D232" t="s">
+        <v>334</v>
+      </c>
+      <c r="E232">
+        <v>72</v>
+      </c>
+      <c r="F232" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>260013704</v>
+      </c>
+      <c r="B233" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C233" t="s">
+        <v>323</v>
+      </c>
+      <c r="D233" t="s">
+        <v>324</v>
+      </c>
+      <c r="E233">
+        <v>120</v>
+      </c>
+      <c r="F233" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>260013705</v>
+      </c>
+      <c r="B234" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C234" t="s">
+        <v>257</v>
+      </c>
+      <c r="D234" t="s">
+        <v>258</v>
+      </c>
+      <c r="E234">
+        <v>45</v>
+      </c>
+      <c r="F234" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>260013705</v>
+      </c>
+      <c r="B235" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C235" t="s">
+        <v>171</v>
+      </c>
+      <c r="D235" t="s">
+        <v>172</v>
+      </c>
+      <c r="E235">
+        <v>31</v>
+      </c>
+      <c r="F235" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>260013705</v>
+      </c>
+      <c r="B236" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C236" t="s">
+        <v>213</v>
+      </c>
+      <c r="D236" t="s">
+        <v>214</v>
+      </c>
+      <c r="E236">
+        <v>124</v>
+      </c>
+      <c r="F236" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>260013706</v>
+      </c>
+      <c r="B237" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C237" t="s">
+        <v>32</v>
+      </c>
+      <c r="D237" t="s">
+        <v>33</v>
+      </c>
+      <c r="E237">
+        <v>32</v>
+      </c>
+      <c r="F237" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>260013706</v>
+      </c>
+      <c r="B238" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C238" t="s">
+        <v>34</v>
+      </c>
+      <c r="D238" t="s">
+        <v>35</v>
+      </c>
+      <c r="E238">
+        <v>28</v>
+      </c>
+      <c r="F238" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <v>260013706</v>
+      </c>
+      <c r="B239" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C239" t="s">
+        <v>19</v>
+      </c>
+      <c r="D239" t="s">
+        <v>20</v>
+      </c>
+      <c r="E239">
+        <v>32</v>
+      </c>
+      <c r="F239" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>260013706</v>
+      </c>
+      <c r="B240" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C240" t="s">
+        <v>21</v>
+      </c>
+      <c r="D240" t="s">
+        <v>22</v>
+      </c>
+      <c r="E240">
+        <v>27</v>
+      </c>
+      <c r="F240" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <v>260013706</v>
+      </c>
+      <c r="B241" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C241" t="s">
+        <v>64</v>
+      </c>
+      <c r="D241" t="s">
+        <v>336</v>
+      </c>
+      <c r="E241">
+        <v>9</v>
+      </c>
+      <c r="F241" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <v>260013706</v>
+      </c>
+      <c r="B242" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>335</v>
+      </c>
+      <c r="E242">
+        <v>32</v>
+      </c>
+      <c r="F242" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <v>260013706</v>
+      </c>
+      <c r="B243" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C243" t="s">
+        <v>62</v>
+      </c>
+      <c r="D243" t="s">
+        <v>63</v>
+      </c>
+      <c r="E243">
+        <v>40</v>
+      </c>
+      <c r="F243" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <v>260013706</v>
+      </c>
+      <c r="B244" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C244" t="s">
+        <v>58</v>
+      </c>
+      <c r="D244" t="s">
+        <v>59</v>
+      </c>
+      <c r="E244">
+        <v>24</v>
+      </c>
+      <c r="F244" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <v>260013706</v>
+      </c>
+      <c r="B245" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C245" t="s">
+        <v>50</v>
+      </c>
+      <c r="D245" t="s">
+        <v>51</v>
+      </c>
+      <c r="E245">
+        <v>50</v>
+      </c>
+      <c r="F245" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <v>260013706</v>
+      </c>
+      <c r="B246" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C246" t="s">
+        <v>54</v>
+      </c>
+      <c r="D246" t="s">
+        <v>55</v>
+      </c>
+      <c r="E246">
+        <v>40</v>
+      </c>
+      <c r="F246" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A247">
+        <v>260013706</v>
+      </c>
+      <c r="B247" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C247" t="s">
+        <v>56</v>
+      </c>
+      <c r="D247" t="s">
+        <v>57</v>
+      </c>
+      <c r="E247">
+        <v>8</v>
+      </c>
+      <c r="F247" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A248">
+        <v>260013707</v>
+      </c>
+      <c r="B248" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C248" t="s">
+        <v>337</v>
+      </c>
+      <c r="D248" t="s">
+        <v>338</v>
+      </c>
+      <c r="E248">
+        <v>32</v>
+      </c>
+      <c r="F248" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A249">
+        <v>260013707</v>
+      </c>
+      <c r="B249" s="5">
+        <v>46162</v>
+      </c>
+      <c r="C249" t="s">
+        <v>8</v>
+      </c>
+      <c r="D249" t="s">
+        <v>9</v>
+      </c>
+      <c r="E249">
+        <v>36</v>
+      </c>
+      <c r="F249" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A250">
+        <v>260013793</v>
+      </c>
+      <c r="B250" s="5">
+        <v>46163</v>
+      </c>
+      <c r="C250" t="s">
+        <v>56</v>
+      </c>
+      <c r="D250" t="s">
+        <v>57</v>
+      </c>
+      <c r="E250">
+        <v>2</v>
+      </c>
+      <c r="F250" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A251">
+        <v>260013793</v>
+      </c>
+      <c r="B251" s="5">
+        <v>46163</v>
+      </c>
+      <c r="C251" t="s">
+        <v>60</v>
+      </c>
+      <c r="D251" t="s">
+        <v>61</v>
+      </c>
+      <c r="E251">
+        <v>18</v>
+      </c>
+      <c r="F251" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A252">
+        <v>260013793</v>
+      </c>
+      <c r="B252" s="5">
+        <v>46163</v>
+      </c>
+      <c r="C252" t="s">
+        <v>17</v>
+      </c>
+      <c r="D252" t="s">
+        <v>18</v>
+      </c>
+      <c r="E252">
         <v>12</v>
       </c>
+      <c r="F252" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A253">
+        <v>260013793</v>
+      </c>
+      <c r="B253" s="5">
+        <v>46163</v>
+      </c>
+      <c r="C253" t="s">
+        <v>13</v>
+      </c>
+      <c r="D253" t="s">
+        <v>14</v>
+      </c>
+      <c r="E253">
+        <v>5</v>
+      </c>
+      <c r="F253" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <v>260013793</v>
+      </c>
+      <c r="B254" s="5">
+        <v>46163</v>
+      </c>
+      <c r="C254" t="s">
+        <v>23</v>
+      </c>
+      <c r="D254" t="s">
+        <v>24</v>
+      </c>
+      <c r="E254">
+        <v>12</v>
+      </c>
+      <c r="F254" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <v>260013793</v>
+      </c>
+      <c r="B255" s="5">
+        <v>46163</v>
+      </c>
+      <c r="C255" t="s">
+        <v>38</v>
+      </c>
+      <c r="D255" t="s">
+        <v>39</v>
+      </c>
+      <c r="E255">
+        <v>12</v>
+      </c>
+      <c r="F255" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <v>260013793</v>
+      </c>
+      <c r="B256" s="5">
+        <v>46163</v>
+      </c>
+      <c r="C256" t="s">
+        <v>8</v>
+      </c>
+      <c r="D256" t="s">
+        <v>9</v>
+      </c>
+      <c r="E256">
+        <v>24</v>
+      </c>
+      <c r="F256" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F206" xr:uid="{AE566383-DF02-41BC-AAA0-951645C6972E}"/>
+  <autoFilter ref="A1:F249" xr:uid="{AE566383-DF02-41BC-AAA0-951645C6972E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>